--- a/src/file/shablonProducts.xlsx
+++ b/src/file/shablonProducts.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OLIM\Downloads\Telegram Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Big_Project\optimit\src\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
   <si>
     <t>BRAND</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>BO'LIM</t>
+  </si>
+  <si>
+    <t>CODE</t>
   </si>
 </sst>
 </file>
@@ -177,7 +180,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,6 +199,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -209,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -219,6 +228,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -499,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="28.21875" bestFit="1" customWidth="1"/>
@@ -515,7 +525,7 @@
     <col min="12" max="12" width="12.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>3</v>
       </c>
@@ -552,8 +562,14 @@
       <c r="L1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="5"/>
       <c r="C2" s="3"/>
@@ -561,7 +577,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="5"/>
       <c r="C3" s="3"/>
@@ -569,7 +585,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="5"/>
       <c r="C4" s="3"/>
@@ -577,7 +593,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="5"/>
       <c r="C5" s="3"/>
@@ -585,7 +601,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="5"/>
       <c r="C6" s="3"/>
@@ -593,7 +609,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="5"/>
       <c r="C7" s="3"/>
@@ -601,7 +617,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="5"/>
       <c r="C8" s="3"/>
@@ -609,7 +625,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="5"/>
       <c r="C9" s="4"/>
@@ -617,7 +633,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="5"/>
       <c r="C10" s="3"/>
@@ -625,7 +641,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="5"/>
       <c r="C11" s="3"/>
@@ -633,7 +649,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="5"/>
       <c r="C12" s="3"/>
@@ -641,7 +657,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="5"/>
       <c r="C13" s="3"/>
@@ -649,7 +665,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="5"/>
       <c r="C14" s="3"/>
@@ -657,7 +673,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="5"/>
       <c r="C15" s="4"/>
@@ -665,7 +681,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="5"/>
       <c r="C16" s="3"/>
